--- a/doc/AtariFA_Lamps.xlsx
+++ b/doc/AtariFA_Lamps.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Projekte\FPGA Atari\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Projekte\FPGA Atari\AtariFA\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0F24BA-572A-451D-9ADA-9E3FDC5BED8C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F303F234-0214-4D21-96A6-BE2453E7E0E1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="aktuell" sheetId="1" r:id="rId1"/>
+    <sheet name="alt" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="39">
   <si>
     <t>Latch</t>
   </si>
@@ -165,12 +166,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -185,10 +192,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -510,6 +521,1396 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="3">
+        <v>16</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1008</v>
+      </c>
+      <c r="I3" s="3">
+        <v>2</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="3">
+        <v>16</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1008</v>
+      </c>
+      <c r="I4" s="3">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>1004</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>1004</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="3">
+        <v>17</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>1004</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
+      <c r="G10" s="3">
+        <v>17</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1008</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="4">
+        <v>3</v>
+      </c>
+      <c r="G11" s="3">
+        <v>17</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I11" s="3">
+        <v>3</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1008</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="4">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3">
+        <v>17</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I12" s="3">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>8</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1008</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="4">
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <v>18</v>
+      </c>
+      <c r="H13">
+        <v>1004</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>8</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1008</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="4">
+        <v>6</v>
+      </c>
+      <c r="G14">
+        <v>18</v>
+      </c>
+      <c r="H14">
+        <v>1004</v>
+      </c>
+      <c r="I14">
+        <v>3</v>
+      </c>
+      <c r="J14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="2">
+        <v>7</v>
+      </c>
+      <c r="G15">
+        <v>18</v>
+      </c>
+      <c r="H15">
+        <v>1004</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
+      </c>
+      <c r="J15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="2">
+        <v>8</v>
+      </c>
+      <c r="G16">
+        <v>18</v>
+      </c>
+      <c r="H16">
+        <v>1004</v>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
+      <c r="J16" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="3">
+        <v>10</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1008</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="3">
+        <v>10</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1008</v>
+      </c>
+      <c r="I18" s="3">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>3</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="3">
+        <v>10</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1008</v>
+      </c>
+      <c r="I19" s="3">
+        <v>3</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>3</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="3">
+        <v>10</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1008</v>
+      </c>
+      <c r="I20" s="3">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>3</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21">
+        <v>21</v>
+      </c>
+      <c r="H21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21">
+        <v>3</v>
+      </c>
+      <c r="J21" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>3</v>
+      </c>
+      <c r="B22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22">
+        <v>21</v>
+      </c>
+      <c r="H22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22">
+        <v>3</v>
+      </c>
+      <c r="J22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>4</v>
+      </c>
+      <c r="B23">
+        <v>1004</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23">
+        <v>21</v>
+      </c>
+      <c r="H23" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23">
+        <v>3</v>
+      </c>
+      <c r="J23" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>4</v>
+      </c>
+      <c r="B24">
+        <v>1004</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="2">
+        <v>9</v>
+      </c>
+      <c r="G24">
+        <v>21</v>
+      </c>
+      <c r="H24" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="J24" t="s">
+        <v>36</v>
+      </c>
+      <c r="K24" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>4</v>
+      </c>
+      <c r="B25">
+        <v>1004</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="2">
+        <v>10</v>
+      </c>
+      <c r="G25" s="3">
+        <v>20</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I25" s="3">
+        <v>4</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K25" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1004</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="2">
+        <v>11</v>
+      </c>
+      <c r="G26" s="3">
+        <v>20</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K26" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>5</v>
+      </c>
+      <c r="B27" s="3">
+        <v>1008</v>
+      </c>
+      <c r="C27" s="3">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="4">
+        <v>12</v>
+      </c>
+      <c r="G27" s="3">
+        <v>20</v>
+      </c>
+      <c r="H27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K27" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>5</v>
+      </c>
+      <c r="B28" s="3">
+        <v>1008</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="4">
+        <v>13</v>
+      </c>
+      <c r="G28" s="3">
+        <v>20</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I28" s="3">
+        <v>4</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K28" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>5</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1008</v>
+      </c>
+      <c r="C29" s="3">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="4">
+        <v>14</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>1004</v>
+      </c>
+      <c r="I29">
+        <v>4</v>
+      </c>
+      <c r="J29" t="s">
+        <v>36</v>
+      </c>
+      <c r="K29" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>5</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1008</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="4">
+        <v>15</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>1004</v>
+      </c>
+      <c r="I30">
+        <v>4</v>
+      </c>
+      <c r="J30" t="s">
+        <v>36</v>
+      </c>
+      <c r="K30" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>1004</v>
+      </c>
+      <c r="I31">
+        <v>4</v>
+      </c>
+      <c r="J31" t="s">
+        <v>37</v>
+      </c>
+      <c r="K31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>1004</v>
+      </c>
+      <c r="I32">
+        <v>4</v>
+      </c>
+      <c r="J32" t="s">
+        <v>37</v>
+      </c>
+      <c r="K32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" s="3">
+        <v>12</v>
+      </c>
+      <c r="H33" s="3">
+        <v>1008</v>
+      </c>
+      <c r="I33" s="3">
+        <v>4</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="3">
+        <v>12</v>
+      </c>
+      <c r="H34" s="3">
+        <v>1008</v>
+      </c>
+      <c r="I34" s="3">
+        <v>4</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>14</v>
+      </c>
+      <c r="B35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C35" s="3">
+        <v>2</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" s="3">
+        <v>12</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1008</v>
+      </c>
+      <c r="I35" s="3">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>14</v>
+      </c>
+      <c r="B36" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C36" s="3">
+        <v>2</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G36" s="3">
+        <v>12</v>
+      </c>
+      <c r="H36" s="3">
+        <v>1008</v>
+      </c>
+      <c r="I36" s="3">
+        <v>4</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>14</v>
+      </c>
+      <c r="B37" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C37" s="3">
+        <v>2</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G37">
+        <v>11</v>
+      </c>
+      <c r="H37" t="s">
+        <v>27</v>
+      </c>
+      <c r="I37">
+        <v>4</v>
+      </c>
+      <c r="J37" t="s">
+        <v>37</v>
+      </c>
+      <c r="K37" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>14</v>
+      </c>
+      <c r="B38" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C38" s="3">
+        <v>2</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" s="4">
+        <v>16</v>
+      </c>
+      <c r="G38">
+        <v>11</v>
+      </c>
+      <c r="H38" t="s">
+        <v>27</v>
+      </c>
+      <c r="I38">
+        <v>4</v>
+      </c>
+      <c r="J38" t="s">
+        <v>38</v>
+      </c>
+      <c r="K38" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>15</v>
+      </c>
+      <c r="B39">
+        <v>1004</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" s="2">
+        <v>17</v>
+      </c>
+      <c r="G39">
+        <v>11</v>
+      </c>
+      <c r="H39" t="s">
+        <v>27</v>
+      </c>
+      <c r="I39">
+        <v>4</v>
+      </c>
+      <c r="J39" t="s">
+        <v>38</v>
+      </c>
+      <c r="K39" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>15</v>
+      </c>
+      <c r="B40">
+        <v>1004</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" s="2">
+        <v>18</v>
+      </c>
+      <c r="G40">
+        <v>11</v>
+      </c>
+      <c r="H40" t="s">
+        <v>27</v>
+      </c>
+      <c r="I40">
+        <v>4</v>
+      </c>
+      <c r="J40" t="s">
+        <v>38</v>
+      </c>
+      <c r="K40" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>15</v>
+      </c>
+      <c r="B41">
+        <v>1004</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" s="2">
+        <v>19</v>
+      </c>
+      <c r="G41" s="3">
+        <v>9</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I41" s="3">
+        <v>5</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K41" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>15</v>
+      </c>
+      <c r="B42">
+        <v>1004</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" s="2">
+        <v>20</v>
+      </c>
+      <c r="G42" s="3">
+        <v>9</v>
+      </c>
+      <c r="H42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I42" s="3">
+        <v>5</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K42" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>16</v>
+      </c>
+      <c r="B43" s="3">
+        <v>1008</v>
+      </c>
+      <c r="C43" s="3">
+        <v>2</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" s="4">
+        <v>21</v>
+      </c>
+      <c r="G43" s="3">
+        <v>9</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I43" s="3">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K43" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>16</v>
+      </c>
+      <c r="B44" s="3">
+        <v>1008</v>
+      </c>
+      <c r="C44" s="3">
+        <v>2</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" s="4">
+        <v>22</v>
+      </c>
+      <c r="G44" s="3">
+        <v>9</v>
+      </c>
+      <c r="H44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I44" s="3">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K44" s="4">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BAE9686-DD5B-42CF-8602-C429740FDBBC}">
+  <dimension ref="A2:K44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="3.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>595</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1">
+        <v>595</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
